--- a/Overture-Match-Suggestions/QA.xlsx
+++ b/Overture-Match-Suggestions/QA.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AH88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,75 +506,82 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>fixlater</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Direct Subtype</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Direct Admin</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Direct Region ISO</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Direct Primary</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>County Subtype</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>County Admin</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>County Region ISO</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>County Primary</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Region Subtype</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Region Admin</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Region Region ISO</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Region Primary</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Resolved Region ISO</t>
         </is>
@@ -623,13 +630,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
@@ -639,15 +660,18 @@
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -692,13 +716,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
@@ -708,15 +746,18 @@
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
       <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -761,13 +802,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
@@ -777,15 +832,18 @@
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -830,13 +888,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
@@ -846,15 +918,18 @@
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -899,13 +974,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
@@ -915,15 +1004,18 @@
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -968,13 +1060,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
       <c r="T7" s="2" t="inlineStr"/>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
@@ -984,15 +1090,18 @@
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr"/>
       <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1037,13 +1146,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="inlineStr"/>
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr"/>
@@ -1053,15 +1176,18 @@
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1106,13 +1232,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr"/>
@@ -1122,15 +1262,18 @@
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1175,13 +1318,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr"/>
@@ -1191,15 +1348,18 @@
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1244,13 +1404,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="inlineStr"/>
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr"/>
@@ -1260,15 +1434,18 @@
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
       <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1313,13 +1490,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr"/>
@@ -1329,15 +1520,18 @@
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
       <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1382,13 +1576,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
@@ -1398,15 +1606,18 @@
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
       <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1451,13 +1662,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
@@ -1467,15 +1692,18 @@
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
       <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1520,13 +1748,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr"/>
@@ -1536,15 +1778,18 @@
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
       <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1589,13 +1834,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr"/>
@@ -1605,15 +1864,18 @@
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1658,13 +1920,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr"/>
@@ -1674,15 +1950,18 @@
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
       <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1727,13 +2006,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr"/>
@@ -1743,15 +2036,18 @@
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
       <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1796,13 +2092,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr"/>
@@ -1812,15 +2122,18 @@
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="inlineStr"/>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
       <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1865,13 +2178,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr"/>
@@ -1881,15 +2208,18 @@
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="inlineStr"/>
       <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1934,13 +2264,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr"/>
@@ -1950,15 +2294,18 @@
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="inlineStr"/>
       <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
       <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2003,13 +2350,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr"/>
@@ -2019,15 +2380,18 @@
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="inlineStr"/>
       <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
       <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2072,13 +2436,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr"/>
@@ -2088,15 +2466,18 @@
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="inlineStr"/>
       <c r="AB23" s="2" t="inlineStr"/>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
       <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2141,13 +2522,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr"/>
@@ -2157,15 +2552,18 @@
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="inlineStr"/>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
       <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2210,13 +2608,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr"/>
@@ -2226,15 +2638,18 @@
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="inlineStr"/>
       <c r="AB25" s="2" t="inlineStr"/>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
       <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2279,13 +2694,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr"/>
@@ -2295,15 +2724,18 @@
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="inlineStr"/>
       <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
       <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2348,13 +2780,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr"/>
@@ -2364,15 +2810,18 @@
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="inlineStr"/>
       <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
       <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2417,13 +2866,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr"/>
@@ -2433,15 +2896,18 @@
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="inlineStr"/>
       <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
       <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2486,13 +2952,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr"/>
@@ -2502,15 +2982,18 @@
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="inlineStr"/>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD29" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
       <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2555,13 +3038,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr"/>
@@ -2571,15 +3068,18 @@
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
       <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2624,13 +3124,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr"/>
@@ -2640,15 +3154,18 @@
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
       <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2693,13 +3210,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr"/>
@@ -2709,15 +3240,18 @@
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="inlineStr"/>
       <c r="AB32" s="2" t="inlineStr"/>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
       <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2762,13 +3296,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr"/>
@@ -2778,15 +3326,18 @@
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="inlineStr"/>
-      <c r="AC33" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
       <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2831,13 +3382,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr"/>
@@ -2847,15 +3412,18 @@
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="inlineStr"/>
       <c r="AB34" s="2" t="inlineStr"/>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2900,13 +3468,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr"/>
@@ -2916,15 +3498,18 @@
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="inlineStr"/>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
       <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2969,13 +3554,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr"/>
@@ -2985,15 +3584,18 @@
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="inlineStr"/>
       <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
       <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3038,13 +3640,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="inlineStr"/>
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr"/>
@@ -3054,15 +3670,18 @@
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="inlineStr"/>
       <c r="AB37" s="2" t="inlineStr"/>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
       <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3107,13 +3726,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr"/>
@@ -3123,15 +3756,18 @@
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="inlineStr"/>
       <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
       <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3176,13 +3812,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr"/>
@@ -3192,15 +3842,18 @@
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="inlineStr"/>
       <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
       <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3245,13 +3898,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr"/>
@@ -3261,15 +3928,18 @@
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="inlineStr"/>
       <c r="AB40" s="2" t="inlineStr"/>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3314,13 +3984,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr"/>
@@ -3330,15 +4014,18 @@
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="inlineStr"/>
       <c r="AB41" s="2" t="inlineStr"/>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
       <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3383,13 +4070,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr"/>
@@ -3399,15 +4100,18 @@
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
       <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3452,13 +4156,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr"/>
@@ -3468,15 +4186,18 @@
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="inlineStr"/>
       <c r="AB43" s="2" t="inlineStr"/>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD43" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
       <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3521,13 +4242,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr"/>
@@ -3537,15 +4272,18 @@
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="inlineStr"/>
       <c r="AB44" s="2" t="inlineStr"/>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
       <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3590,13 +4328,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr"/>
@@ -3606,15 +4358,18 @@
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="inlineStr"/>
       <c r="AB45" s="2" t="inlineStr"/>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD45" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
       <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3659,13 +4414,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr"/>
@@ -3675,15 +4444,18 @@
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="inlineStr"/>
       <c r="AB46" s="2" t="inlineStr"/>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
       <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3728,13 +4500,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr"/>
@@ -3744,15 +4530,18 @@
       <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="inlineStr"/>
       <c r="AB47" s="2" t="inlineStr"/>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
       <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3797,13 +4586,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n"/>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="n"/>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr"/>
@@ -3813,15 +4616,18 @@
       <c r="Z48" s="2" t="inlineStr"/>
       <c r="AA48" s="2" t="inlineStr"/>
       <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
       <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3866,13 +4672,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
-      <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr"/>
@@ -3882,15 +4702,18 @@
       <c r="Z49" s="2" t="inlineStr"/>
       <c r="AA49" s="2" t="inlineStr"/>
       <c r="AB49" s="2" t="inlineStr"/>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
       <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3935,13 +4758,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="n"/>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr"/>
@@ -3951,15 +4788,18 @@
       <c r="Z50" s="2" t="inlineStr"/>
       <c r="AA50" s="2" t="inlineStr"/>
       <c r="AB50" s="2" t="inlineStr"/>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
       <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4004,13 +4844,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n"/>
-      <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="n"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="n"/>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr"/>
@@ -4020,15 +4874,18 @@
       <c r="Z51" s="2" t="inlineStr"/>
       <c r="AA51" s="2" t="inlineStr"/>
       <c r="AB51" s="2" t="inlineStr"/>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
       <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4073,13 +4930,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr"/>
@@ -4089,15 +4960,18 @@
       <c r="Z52" s="2" t="inlineStr"/>
       <c r="AA52" s="2" t="inlineStr"/>
       <c r="AB52" s="2" t="inlineStr"/>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
       <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4142,13 +5016,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr"/>
@@ -4158,15 +5046,18 @@
       <c r="Z53" s="2" t="inlineStr"/>
       <c r="AA53" s="2" t="inlineStr"/>
       <c r="AB53" s="2" t="inlineStr"/>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD53" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
       <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4211,13 +5102,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr"/>
@@ -4227,15 +5132,18 @@
       <c r="Z54" s="2" t="inlineStr"/>
       <c r="AA54" s="2" t="inlineStr"/>
       <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
       <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4280,13 +5188,27 @@
           <t>Ad-Dawḥah [Doha]Qatar</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="n"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>QA-DA</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>الدوحة</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr"/>
@@ -4296,15 +5218,18 @@
       <c r="Z55" s="2" t="inlineStr"/>
       <c r="AA55" s="2" t="inlineStr"/>
       <c r="AB55" s="2" t="inlineStr"/>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD55" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
       <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4349,13 +5274,27 @@
           <t>Aḍ-Ḍ'āyan [Al Daayen]Qatar</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>QA-ZA</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>الضعاين</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr"/>
@@ -4365,15 +5304,18 @@
       <c r="Z56" s="2" t="inlineStr"/>
       <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr"/>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
       <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4418,13 +5360,27 @@
           <t>Aḍ-Ḍ'āyan [Al Daayen]Qatar</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>QA-ZA</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>الضعاين</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr"/>
@@ -4434,15 +5390,18 @@
       <c r="Z57" s="2" t="inlineStr"/>
       <c r="AA57" s="2" t="inlineStr"/>
       <c r="AB57" s="2" t="inlineStr"/>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD57" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
       <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4487,13 +5446,27 @@
           <t>Al-Khawr &amp; Adh-Dhakhīrah  [Al Khor]Qatar</t>
         </is>
       </c>
-      <c r="M58" s="2" t="n"/>
-      <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="n"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>QA-KH</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>الخور والذخيرة</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="n"/>
+      <c r="R58" s="2" t="n"/>
+      <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr"/>
@@ -4503,15 +5476,18 @@
       <c r="Z58" s="2" t="inlineStr"/>
       <c r="AA58" s="2" t="inlineStr"/>
       <c r="AB58" s="2" t="inlineStr"/>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
       <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4556,13 +5532,27 @@
           <t>Al-Khawr &amp; Adh-Dhakhīrah  [Al Khor]Qatar</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n"/>
-      <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="n"/>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
-      <c r="S59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>QA-KH</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>الخور والذخيرة</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="n"/>
+      <c r="R59" s="2" t="n"/>
+      <c r="S59" s="2" t="n"/>
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr"/>
@@ -4572,15 +5562,18 @@
       <c r="Z59" s="2" t="inlineStr"/>
       <c r="AA59" s="2" t="inlineStr"/>
       <c r="AB59" s="2" t="inlineStr"/>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD59" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
       <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4625,13 +5618,27 @@
           <t>Al-Khawr &amp; Adh-Dhakhīrah  [Al Khor]Qatar</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
-      <c r="S60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>QA-KH</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>الخور والذخيرة</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="n"/>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr"/>
@@ -4641,15 +5648,18 @@
       <c r="Z60" s="2" t="inlineStr"/>
       <c r="AA60" s="2" t="inlineStr"/>
       <c r="AB60" s="2" t="inlineStr"/>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
       <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4694,45 +5704,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="n"/>
+      <c r="R61" s="2" t="n"/>
+      <c r="S61" s="2" t="n"/>
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr"/>
       <c r="W61" s="2" t="inlineStr"/>
       <c r="X61" s="2" t="inlineStr"/>
-      <c r="Y61" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA61" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
+      <c r="AE61" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="2" t="inlineStr">
+      <c r="AF61" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -4781,45 +5808,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="n"/>
+      <c r="R62" s="2" t="n"/>
+      <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr"/>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr"/>
-      <c r="Y62" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
+      <c r="AE62" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="2" t="inlineStr">
+      <c r="AF62" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -4868,45 +5912,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="n"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr"/>
-      <c r="S63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="n"/>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="n"/>
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr"/>
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr"/>
-      <c r="Y63" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AE63" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="2" t="inlineStr">
+      <c r="AF63" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -4955,45 +6016,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr"/>
-      <c r="S64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="n"/>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr"/>
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr"/>
-      <c r="Y64" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
+      <c r="AE64" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="2" t="inlineStr">
+      <c r="AF64" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -5042,45 +6120,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="inlineStr"/>
-      <c r="R65" s="2" t="inlineStr"/>
-      <c r="S65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="n"/>
+      <c r="R65" s="2" t="n"/>
+      <c r="S65" s="2" t="n"/>
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr"/>
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr"/>
-      <c r="Y65" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
+      <c r="AE65" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" s="2" t="inlineStr">
+      <c r="AF65" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -5129,45 +6224,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="2" t="inlineStr"/>
-      <c r="S66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="n"/>
+      <c r="R66" s="2" t="n"/>
+      <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="inlineStr"/>
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr"/>
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr"/>
-      <c r="Y66" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
+      <c r="AE66" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="2" t="inlineStr">
+      <c r="AF66" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -5216,45 +6328,62 @@
           <t>Al-WakrahQatar</t>
         </is>
       </c>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="n"/>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr"/>
-      <c r="S67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>QA-WA</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>الوكرة</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="n"/>
+      <c r="R67" s="2" t="n"/>
+      <c r="S67" s="2" t="n"/>
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr"/>
       <c r="W67" s="2" t="inlineStr"/>
       <c r="X67" s="2" t="inlineStr"/>
-      <c r="Y67" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
+      <c r="AE67" s="2" t="inlineStr">
         <is>
           <t>الوكرة</t>
         </is>
       </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="2" t="inlineStr">
+      <c r="AF67" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="2" t="inlineStr">
         <is>
           <t>QA-WA</t>
         </is>
@@ -5303,45 +6432,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="n"/>
+      <c r="R68" s="2" t="n"/>
+      <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr"/>
       <c r="W68" s="2" t="inlineStr"/>
       <c r="X68" s="2" t="inlineStr"/>
-      <c r="Y68" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AE68" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" s="2" t="inlineStr">
+      <c r="AF68" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5390,45 +6536,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
-      <c r="S69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="n"/>
+      <c r="R69" s="2" t="n"/>
+      <c r="S69" s="2" t="n"/>
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr"/>
       <c r="W69" s="2" t="inlineStr"/>
       <c r="X69" s="2" t="inlineStr"/>
-      <c r="Y69" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
+      <c r="AE69" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" s="2" t="inlineStr">
+      <c r="AF69" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5477,45 +6640,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M70" s="2" t="n"/>
-      <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="n"/>
+      <c r="R70" s="2" t="n"/>
+      <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr"/>
       <c r="W70" s="2" t="inlineStr"/>
       <c r="X70" s="2" t="inlineStr"/>
-      <c r="Y70" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
+      <c r="AE70" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="2" t="inlineStr">
+      <c r="AF70" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5564,45 +6744,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="n"/>
+      <c r="R71" s="2" t="n"/>
+      <c r="S71" s="2" t="n"/>
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr"/>
       <c r="W71" s="2" t="inlineStr"/>
       <c r="X71" s="2" t="inlineStr"/>
-      <c r="Y71" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AE71" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" s="2" t="inlineStr">
+      <c r="AF71" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5651,45 +6848,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M72" s="2" t="n"/>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="n"/>
+      <c r="R72" s="2" t="n"/>
+      <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr"/>
       <c r="W72" s="2" t="inlineStr"/>
       <c r="X72" s="2" t="inlineStr"/>
-      <c r="Y72" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AE72" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" s="2" t="inlineStr">
+      <c r="AF72" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5738,45 +6952,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n"/>
-      <c r="N73" s="2" t="n"/>
-      <c r="O73" s="2" t="n"/>
-      <c r="P73" s="2" t="n"/>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="n"/>
+      <c r="R73" s="2" t="n"/>
+      <c r="S73" s="2" t="n"/>
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr"/>
       <c r="W73" s="2" t="inlineStr"/>
       <c r="X73" s="2" t="inlineStr"/>
-      <c r="Y73" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AE73" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" s="2" t="inlineStr">
+      <c r="AF73" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5825,45 +7056,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="n"/>
+      <c r="R74" s="2" t="n"/>
+      <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr"/>
       <c r="W74" s="2" t="inlineStr"/>
       <c r="X74" s="2" t="inlineStr"/>
-      <c r="Y74" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
+      <c r="AE74" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" s="2" t="inlineStr">
+      <c r="AF74" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5912,45 +7160,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n"/>
-      <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="inlineStr"/>
-      <c r="R75" s="2" t="inlineStr"/>
-      <c r="S75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="n"/>
+      <c r="R75" s="2" t="n"/>
+      <c r="S75" s="2" t="n"/>
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr"/>
       <c r="W75" s="2" t="inlineStr"/>
       <c r="X75" s="2" t="inlineStr"/>
-      <c r="Y75" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AE75" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="2" t="inlineStr">
+      <c r="AF75" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -5999,45 +7264,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M76" s="2" t="n"/>
-      <c r="N76" s="2" t="n"/>
-      <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
-      <c r="S76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="n"/>
+      <c r="R76" s="2" t="n"/>
+      <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr"/>
       <c r="W76" s="2" t="inlineStr"/>
       <c r="X76" s="2" t="inlineStr"/>
-      <c r="Y76" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AE76" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="2" t="inlineStr">
+      <c r="AF76" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -6086,45 +7368,62 @@
           <t>Ar-RayyānQatar</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="2" t="inlineStr"/>
-      <c r="S77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>QA-RA</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="n"/>
+      <c r="R77" s="2" t="n"/>
+      <c r="S77" s="2" t="n"/>
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr"/>
       <c r="W77" s="2" t="inlineStr"/>
       <c r="X77" s="2" t="inlineStr"/>
-      <c r="Y77" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
+      <c r="AE77" s="2" t="inlineStr">
         <is>
           <t>الريان</t>
         </is>
       </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="2" t="inlineStr">
+      <c r="AF77" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="2" t="inlineStr">
         <is>
           <t>QA-RA</t>
         </is>
@@ -6173,13 +7472,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M78" s="2" t="n"/>
-      <c r="N78" s="2" t="n"/>
-      <c r="O78" s="2" t="n"/>
-      <c r="P78" s="2" t="n"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
-      <c r="S78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="n"/>
+      <c r="R78" s="2" t="n"/>
+      <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr"/>
@@ -6189,15 +7502,18 @@
       <c r="Z78" s="2" t="inlineStr"/>
       <c r="AA78" s="2" t="inlineStr"/>
       <c r="AB78" s="2" t="inlineStr"/>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
       <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6242,13 +7558,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
-      <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="n"/>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr"/>
-      <c r="S79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="n"/>
+      <c r="R79" s="2" t="n"/>
+      <c r="S79" s="2" t="n"/>
       <c r="T79" s="2" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr"/>
@@ -6258,15 +7588,18 @@
       <c r="Z79" s="2" t="inlineStr"/>
       <c r="AA79" s="2" t="inlineStr"/>
       <c r="AB79" s="2" t="inlineStr"/>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD79" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
       <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6305,13 +7638,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M80" s="2" t="n"/>
-      <c r="N80" s="2" t="n"/>
-      <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr"/>
-      <c r="S80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="n"/>
+      <c r="R80" s="2" t="n"/>
+      <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr"/>
@@ -6321,15 +7668,18 @@
       <c r="Z80" s="2" t="inlineStr"/>
       <c r="AA80" s="2" t="inlineStr"/>
       <c r="AB80" s="2" t="inlineStr"/>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
       <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6368,13 +7718,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n"/>
-      <c r="N81" s="2" t="n"/>
-      <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
-      <c r="Q81" s="2" t="inlineStr"/>
-      <c r="R81" s="2" t="inlineStr"/>
-      <c r="S81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="n"/>
+      <c r="R81" s="2" t="n"/>
+      <c r="S81" s="2" t="n"/>
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr"/>
@@ -6384,15 +7748,18 @@
       <c r="Z81" s="2" t="inlineStr"/>
       <c r="AA81" s="2" t="inlineStr"/>
       <c r="AB81" s="2" t="inlineStr"/>
-      <c r="AC81" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD81" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
       <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6431,13 +7798,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M82" s="2" t="n"/>
-      <c r="N82" s="2" t="n"/>
-      <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
-      <c r="Q82" s="2" t="inlineStr"/>
-      <c r="R82" s="2" t="inlineStr"/>
-      <c r="S82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="n"/>
+      <c r="R82" s="2" t="n"/>
+      <c r="S82" s="2" t="n"/>
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr"/>
@@ -6447,15 +7828,18 @@
       <c r="Z82" s="2" t="inlineStr"/>
       <c r="AA82" s="2" t="inlineStr"/>
       <c r="AB82" s="2" t="inlineStr"/>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
       <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6494,13 +7878,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n"/>
-      <c r="N83" s="2" t="n"/>
-      <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
-      <c r="Q83" s="2" t="inlineStr"/>
-      <c r="R83" s="2" t="inlineStr"/>
-      <c r="S83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="n"/>
+      <c r="R83" s="2" t="n"/>
+      <c r="S83" s="2" t="n"/>
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr"/>
@@ -6510,15 +7908,18 @@
       <c r="Z83" s="2" t="inlineStr"/>
       <c r="AA83" s="2" t="inlineStr"/>
       <c r="AB83" s="2" t="inlineStr"/>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
       <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6557,13 +7958,27 @@
           <t>Ash-Shaḥāniyah [Al Shahaniya]Qatar</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n"/>
-      <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="2" t="inlineStr"/>
-      <c r="S84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>QA-SH</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>الشحانية</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="n"/>
+      <c r="R84" s="2" t="n"/>
+      <c r="S84" s="2" t="n"/>
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr"/>
@@ -6573,15 +7988,18 @@
       <c r="Z84" s="2" t="inlineStr"/>
       <c r="AA84" s="2" t="inlineStr"/>
       <c r="AB84" s="2" t="inlineStr"/>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD84" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
       <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6626,13 +8044,27 @@
           <t>Ash-ShamālQatar</t>
         </is>
       </c>
-      <c r="M85" s="2" t="n"/>
-      <c r="N85" s="2" t="n"/>
-      <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="2" t="inlineStr"/>
-      <c r="S85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>QA-MS</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>الشمال</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="n"/>
+      <c r="R85" s="2" t="n"/>
+      <c r="S85" s="2" t="n"/>
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr"/>
@@ -6642,15 +8074,18 @@
       <c r="Z85" s="2" t="inlineStr"/>
       <c r="AA85" s="2" t="inlineStr"/>
       <c r="AB85" s="2" t="inlineStr"/>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD85" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
       <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6695,13 +8130,27 @@
           <t>Ash-ShamālQatar</t>
         </is>
       </c>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="2" t="n"/>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="inlineStr"/>
-      <c r="R86" s="2" t="inlineStr"/>
-      <c r="S86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>QA-MS</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>الشمال</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="n"/>
+      <c r="R86" s="2" t="n"/>
+      <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="inlineStr"/>
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr"/>
@@ -6711,15 +8160,18 @@
       <c r="Z86" s="2" t="inlineStr"/>
       <c r="AA86" s="2" t="inlineStr"/>
       <c r="AB86" s="2" t="inlineStr"/>
-      <c r="AC86" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
       <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6764,13 +8216,27 @@
           <t>Ash-ShamālQatar</t>
         </is>
       </c>
-      <c r="M87" s="2" t="n"/>
-      <c r="N87" s="2" t="n"/>
-      <c r="O87" s="2" t="n"/>
-      <c r="P87" s="2" t="n"/>
-      <c r="Q87" s="2" t="inlineStr"/>
-      <c r="R87" s="2" t="inlineStr"/>
-      <c r="S87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>QA-MS</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>الشمال</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="n"/>
+      <c r="R87" s="2" t="n"/>
+      <c r="S87" s="2" t="n"/>
       <c r="T87" s="2" t="inlineStr"/>
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr"/>
@@ -6780,15 +8246,18 @@
       <c r="Z87" s="2" t="inlineStr"/>
       <c r="AA87" s="2" t="inlineStr"/>
       <c r="AB87" s="2" t="inlineStr"/>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD87" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
       <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6833,45 +8302,62 @@
           <t>Umm ṢalālQatar</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n"/>
-      <c r="N88" s="2" t="n"/>
-      <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
-      <c r="S88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>QA-US</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>أم صلال</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="n"/>
+      <c r="R88" s="2" t="n"/>
+      <c r="S88" s="2" t="n"/>
       <c r="T88" s="2" t="inlineStr"/>
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr"/>
       <c r="W88" s="2" t="inlineStr"/>
       <c r="X88" s="2" t="inlineStr"/>
-      <c r="Y88" s="2" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="Z88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
         <is>
           <t>QA-US</t>
         </is>
       </c>
-      <c r="AB88" s="2" t="inlineStr">
+      <c r="AE88" s="2" t="inlineStr">
         <is>
           <t>أم صلال</t>
         </is>
       </c>
-      <c r="AC88" s="2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AD88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="2" t="inlineStr">
+      <c r="AF88" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AG88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="2" t="inlineStr">
         <is>
           <t>QA-US</t>
         </is>
